--- a/Config/Excel/GameConfig/SkillConfig.xlsx
+++ b/Config/Excel/GameConfig/SkillConfig.xlsx
@@ -2,39 +2,375 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="15320" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="SkillConfig" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="21">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,15 +378,305 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -403,7 +1029,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -414,7 +1039,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <cols>
+    <col width="22.9134615384615" customWidth="1" min="3" max="3"/>
+    <col width="24.6730769230769" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -710,10 +1339,10 @@
         <v>11001</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -729,7 +1358,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>玩家默认单体普攻</t>
+          <t>玩家清怪版普攻：更快挥击频率</t>
         </is>
       </c>
     </row>
@@ -766,7 +1395,7 @@
         <v>21001</v>
       </c>
       <c r="K5" t="n">
-        <v>1500</v>
+        <v>1650</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -822,7 +1451,7 @@
         <v>21002</v>
       </c>
       <c r="K6" t="n">
-        <v>1300</v>
+        <v>1450</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -878,7 +1507,7 @@
         <v>21003</v>
       </c>
       <c r="K7" t="n">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>

--- a/Config/Excel/GameConfig/SkillConfig.xlsx
+++ b/Config/Excel/GameConfig/SkillConfig.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <cols>
     <col width="22.9134615384615" customWidth="1" min="3" max="3"/>
@@ -1088,45 +1088,65 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>CastCheckConfigId</t>
+          <t>CooldownGroupId</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>CooldownGroupId</t>
+          <t>CooldownMs</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>CooldownMs</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>CanMoveCast</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>CanMoveCast</t>
+          <t>NeedExplicitTarget</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>NeedExplicitTarget</t>
+          <t>BuffGroupId</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>EffectGroupId</t>
+          <t>IsEnabled</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>IsEnabled</t>
+          <t>ProjectileSpeed</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
+        <is>
+          <t>ProjectileMaxDistance</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ProjectileCollisionRadius</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ProjectilePiercing</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ProjectileMaxHitCount</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
@@ -1175,7 +1195,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>int#ref=SkillCastCheckConfigCategory</t>
+          <t>int</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1190,30 +1210,50 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>int#ref=BuffGroupConfigCategory</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>int#ref=SkillEffectGroupConfigCategory</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1262,45 +1302,65 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>施法校验配置ID</t>
+          <t>冷却组ID</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>冷却组ID</t>
+          <t>冷却毫秒</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>冷却毫秒</t>
+          <t>优先级</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>优先级</t>
+          <t>是否可移动施法</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>是否可移动施法</t>
+          <t>是否必须显式指定目标</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>是否必须显式指定目标</t>
+          <t>效果组ID</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>效果组ID</t>
+          <t>是否启用</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>是否启用</t>
+          <t>投射物飞行速度（单位/秒）</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
+        <is>
+          <t>投射物最大飞行距离</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>投射物碰撞半径</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>投射物是否穿透</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>投射物最大命中单位数</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
@@ -1333,30 +1393,42 @@
         <v>31001</v>
       </c>
       <c r="I4" t="n">
-        <v>41001</v>
+        <v>11001</v>
       </c>
       <c r="J4" t="n">
-        <v>11001</v>
+        <v>550</v>
       </c>
       <c r="K4" t="n">
-        <v>550</v>
-      </c>
-      <c r="L4" t="n">
         <v>1</v>
       </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
       <c r="M4" t="b">
         <v>0</v>
       </c>
-      <c r="N4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="N4" t="n">
         <v>61001</v>
       </c>
-      <c r="P4" t="b">
+      <c r="O4" t="b">
         <v>1</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="P4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>20</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>玩家清怪版普攻：更快挥击频率</t>
         </is>
@@ -1389,30 +1461,42 @@
         <v>31002</v>
       </c>
       <c r="I5" t="n">
-        <v>41002</v>
+        <v>21001</v>
       </c>
       <c r="J5" t="n">
-        <v>21001</v>
+        <v>1650</v>
       </c>
       <c r="K5" t="n">
-        <v>1650</v>
-      </c>
-      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="b">
         <v>0</v>
       </c>
       <c r="M5" t="b">
         <v>0</v>
       </c>
-      <c r="N5" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
+      <c r="N5" t="n">
         <v>61002</v>
       </c>
-      <c r="P5" t="b">
+      <c r="O5" t="b">
         <v>1</v>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="P5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>20</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>普通怪物默认单体普攻</t>
         </is>
@@ -1445,30 +1529,42 @@
         <v>31003</v>
       </c>
       <c r="I6" t="n">
-        <v>41002</v>
+        <v>21002</v>
       </c>
       <c r="J6" t="n">
-        <v>21002</v>
+        <v>1450</v>
       </c>
       <c r="K6" t="n">
-        <v>1450</v>
-      </c>
-      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="b">
         <v>0</v>
       </c>
       <c r="M6" t="b">
         <v>0</v>
       </c>
-      <c r="N6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
+      <c r="N6" t="n">
         <v>61002</v>
       </c>
-      <c r="P6" t="b">
+      <c r="O6" t="b">
         <v>1</v>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="P6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>20</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>精英怪物默认单体普攻</t>
         </is>
@@ -1501,30 +1597,42 @@
         <v>31004</v>
       </c>
       <c r="I7" t="n">
-        <v>41002</v>
+        <v>21003</v>
       </c>
       <c r="J7" t="n">
-        <v>21003</v>
+        <v>1900</v>
       </c>
       <c r="K7" t="n">
-        <v>1900</v>
-      </c>
-      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="b">
         <v>0</v>
       </c>
       <c r="M7" t="b">
         <v>0</v>
       </c>
-      <c r="N7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
+      <c r="N7" t="n">
         <v>61002</v>
       </c>
-      <c r="P7" t="b">
+      <c r="O7" t="b">
         <v>1</v>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="P7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>20</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>Boss默认单体普攻</t>
         </is>
